--- a/assets/forms/box_data.xlsx
+++ b/assets/forms/box_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP ProBook 455 G10\Desktop\project\box-print-web\assets\forms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B6CF4CE-E77D-42E0-B6CA-C1A2190B1EB2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1765E4C5-D10B-40E8-A080-EC382D538915}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135" xr2:uid="{ED468E32-3EE9-4E65-96DA-B982F21E2A02}"/>
   </bookViews>
@@ -758,11 +758,11 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="2">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A23" xr:uid="{784A7E4B-F5A8-4959-9770-27D3ED7FFF78}">
       <formula1>$S$2:$S$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:G23" xr:uid="{D379DA67-29DC-458E-ACEC-581721C737E4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E23 F9:G23" xr:uid="{D379DA67-29DC-458E-ACEC-581721C737E4}">
       <formula1>$T$2:$T$4</formula1>
     </dataValidation>
   </dataValidations>

--- a/assets/forms/box_data.xlsx
+++ b/assets/forms/box_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP ProBook 455 G10\Desktop\project\box-print-web\assets\forms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1765E4C5-D10B-40E8-A080-EC382D538915}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F36A8D8-85C8-459B-B6BD-14E5E0E1DD01}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135" xr2:uid="{ED468E32-3EE9-4E65-96DA-B982F21E2A02}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135" activeTab="1" xr2:uid="{ED468E32-3EE9-4E65-96DA-B982F21E2A02}"/>
   </bookViews>
   <sheets>
     <sheet name="양식" sheetId="1" r:id="rId1"/>
@@ -165,15 +165,15 @@
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>39211</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>124799</xdr:rowOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>10505</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 2">
+        <xdr:cNvPr id="4" name="그림 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7A86766-2DEA-48FA-9317-F23F26F2C4DC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45975BAA-9AAC-4170-9598-C93D8FFDCB25}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -196,7 +196,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="7964011" cy="6982799"/>
+          <a:ext cx="7964011" cy="7020905"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
